--- a/assets/docs/lop1/Hoat dong trai nghiem - Lop 1.xlsx
+++ b/assets/docs/lop1/Hoat dong trai nghiem - Lop 1.xlsx
@@ -724,7 +724,9 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN lập kế hoạch và quản lí chi tiêu, thời gian ở mức đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở phần sinh hoạt theo chủ đề của tiết “SINH HOẠT SAO: SƠ KẾT TUẦN 2 - PHƯƠNG HƯỚNG TUẦN 3”, GV chiếu ảnh chụp giờ học
+Năng lực số Miền 2 (Cơ bản, bậc 1): Ở phần khởi động và đánh giá, GV mở nhạc bài hát Em yêu trường em trên máy để cả lớp hát, vận động
+KNS: KN lập kế hoạch và quản lí chi tiêu, thời gian ở mức đơn giản.</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1320,7 @@
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>NLS-GT (Cơ bản 1): Trong giờ Sinh hoạt Sao sơ kết tuần 8, GV chiếu bảng theo dõi của lớp.
+          <t>Năng lực số Miền 2 (Cơ bản, bậc 1): Trong giờ Sinh hoạt Sao sơ kết tuần 8, GV chiếu bảng theo dõi của lớp và gõ nhận xét của từng sao ngay vào đúng dòng
 KNS: KN lập kế hoạch và quản lí chi tiêu, thời gian ở mức đơn giản.</t>
         </is>
       </c>
@@ -1726,7 +1728,7 @@
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>NLS-GT (Cơ bản 1): Trong giờ Sinh hoạt Sao sơ kết tuần 12, GV chiếu bảng theo dõi của lớp.
+          <t>Năng lực số Miền 2 (Cơ bản, bậc 1): Trong giờ Sinh hoạt Sao sơ kết tuần 12, GV chiếu bảng theo dõi của lớp và gõ nhận xét của từng sao ngay vào đúng dòng
 KNS: KN lập kế hoạch và quản lí chi tiêu, thời gian ở mức đơn giản.</t>
         </is>
       </c>
@@ -1926,7 +1928,7 @@
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>NLS-GT (Cơ bản 1): Trong giờ Sinh hoạt Sao sơ kết tuần 14, GV chiếu bảng theo dõi của lớp.</t>
+          <t>Năng lực số Miền 2 (Cơ bản, bậc 1): Trong giờ Sinh hoạt Sao sơ kết tuần 14, GV chiếu bảng theo dõi của lớp và gõ nhận xét của từng sao ngay vào đúng dòng</t>
         </is>
       </c>
     </row>
@@ -2122,7 +2124,12 @@
           <t>48</t>
         </is>
       </c>
-      <c r="H51" s="4" t="inlineStr"/>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở phần Sơ kết tuần 16, GV chiếu bảng theo dõi thi đua của lớp lên màn hình với các cột đi học đúng giờ, trực nhật, giữ vở sạch
+Năng lực số Miền 2 (Cơ bản, bậc 1): Ở phần Phương hướng tuần 17, GV mở bảng chung còn trống trên màn hình, đại diện các tổ lần lượt lên ghi việc tổ mình nhận làm</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
@@ -2314,7 +2321,12 @@
           <t>54</t>
         </is>
       </c>
-      <c r="H57" s="4" t="inlineStr"/>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở phần Sơ kết tuần 18, GV chiếu bảng theo dõi thi đua của lớp lên màn hình với các cột đi học đúng giờ, trực nhật, giữ vở sạch
+Năng lực số Miền 2 (Cơ bản, bậc 1): Ở phần Phương hướng tuần 19, GV chiếu bộ ảnh bữa ăn hợp vệ sinh và thức ăn để hở ngoài đường gắn với nội dung an toàn thực phẩm</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
@@ -2506,7 +2518,12 @@
           <t>60</t>
         </is>
       </c>
-      <c r="H63" s="4" t="inlineStr"/>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở phần Sơ kết tuần 20, GV chiếu bảng theo dõi thi đua của lớp lên màn hình với các cột đi học đúng giờ, trực nhật, giữ vở sạch, giúp bạn
+Năng lực số Miền 2 (Cơ bản, bậc 1): Ở phần Phương hướng tuần 21, GV mở bảng chung còn trống trên màn hình, đại diện các tổ lần lượt lên ghi việc tổ mình nhận làm</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
@@ -2700,7 +2717,8 @@
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Ở phần Sơ kết tuần 22, GV chiếu bảng theo dõi thi đua của lớp lên màn hình.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở phần Sơ kết tuần 22, GV chiếu bảng theo dõi thi đua của lớp lên màn hình với các cột đi học đúng giờ, trực nhật, giữ vở sạch, giúp bạn
+Năng lực số Miền 2 (Cơ bản, bậc 1): Ở phần Phương hướng tuần 23, GV mở bảng chung còn trống trên màn hình, đại diện các tổ lần lượt lên ghi việc tổ mình nhận làm
 KNS: KN lập kế hoạch và quản lí chi tiêu, thời gian ở mức đơn giản.</t>
         </is>
       </c>
@@ -2901,7 +2919,8 @@
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Ở phần Sơ kết tuần 24, GV chiếu bảng theo dõi thi đua của lớp lên màn hình.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở phần Sơ kết tuần 24, GV chiếu bảng theo dõi thi đua của lớp lên màn hình với các cột đi học đúng giờ, trực nhật, giữ vở sạch, giúp bạn
+Năng lực số Miền 2 (Cơ bản, bậc 1): Ở phần Phương hướng tuần 25, GV mở bảng chung còn trống trên màn hình, đại diện các tổ lần lượt lên ghi việc tổ mình nhận làm
 KNS: KN lập kế hoạch và quản lí chi tiêu, thời gian ở mức đơn giản.</t>
         </is>
       </c>
@@ -3290,7 +3309,12 @@
           <t>84</t>
         </is>
       </c>
-      <c r="H87" s="4" t="inlineStr"/>
+      <c r="H87" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở phần Sơ kết tuần 28, GV chiếu bảng theo dõi thi đua của lớp lên màn hình với các cột đi học đúng giờ, trực nhật, giữ vở sạch, giúp bạn
+Năng lực số Miền 2 (Cơ bản, bậc 1): Ở phần Phương hướng tuần 29, GV mở bảng chung còn trống trên màn hình, đại diện các tổ lần lượt lên ghi việc tổ mình nhận làm</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
@@ -3488,7 +3512,9 @@
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN lập kế hoạch và quản lí chi tiêu, thời gian ở mức đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở phần Sơ kết tuần 30, GV chiếu bảng theo dõi thi đua của lớp lên màn hình với các cột đi học đúng giờ, trực nhật, giữ vở sạch, chăm sóc cây
+Năng lực số Miền 2 (Cơ bản, bậc 1): Ở phần Phương hướng tuần 31, GV mở bảng chung còn trống trên màn hình, đại diện các tổ lần lượt lên ghi việc tổ mình nhận làm
+KNS: KN lập kế hoạch và quản lí chi tiêu, thời gian ở mức đơn giản.</t>
         </is>
       </c>
     </row>

--- a/assets/docs/lop1/Hoat dong trai nghiem - Lop 1.xlsx
+++ b/assets/docs/lop1/Hoat dong trai nghiem - Lop 1.xlsx
@@ -1120,7 +1120,8 @@
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN lập kế hoạch và quản lí chi tiêu, thời gian ở mức đơn giản.</t>
+          <t>Năng lực số Miền 2 (Cơ bản, bậc 1): Trong giờ Sinh hoạt Sao sơ kết tuần 6, GV chiếu bảng theo dõi của lớp lên màn hình và gõ ngay nhận xét của từng sao vào đúng dòng
+KNS: KN lập kế hoạch và quản lí chi tiêu, thời gian ở mức đơn giản.</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1528,8 @@
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN lập kế hoạch và quản lí chi tiêu, thời gian ở mức đơn giản.</t>
+          <t>Năng lực số Miền 2 (Cơ bản, bậc 1): Trong giờ Sinh hoạt Sao sơ kết tuần 10, GV chiếu bảng theo dõi của lớp và gõ nhận xét của từng sao ngay vào đúng dòng
+KNS: KN lập kế hoạch và quản lí chi tiêu, thời gian ở mức đơn giản.</t>
         </is>
       </c>
     </row>
@@ -3721,7 +3723,8 @@
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>NLS-GT (Cơ bản 1): Ở phần Phương hướng tuần 33, GV mở bảng chung còn trống trên màn hình, đại diện các tổ lần lượt lên.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở phần Sơ kết tuần 32, GV chiếu bảng theo dõi thi đua cả năm của lớp lên màn hình, tô màu những tuần lớp làm tốt để HS nhìn thấy sự tiến bộ…
+Năng lực số Miền 2 (Cơ bản, bậc 1): Ở phần Phương hướng tuần 33, GV mở bảng chung còn trống trên màn hình, đại diện các tổ lần lượt lên ghi việc tổ mình nhận làm
 KNS: KN lập kế hoạch và quản lí chi tiêu, thời gian ở mức đơn giản.</t>
         </is>
       </c>
@@ -3927,7 +3930,8 @@
       </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
-          <t>NLS-GT (Cơ bản 1): Ở phần Phương hướng tuần 35, GV mở bảng chung còn trống trên màn hình, đại diện các tổ lần lượt lên.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở phần Sơ kết tuần 34, GV chiếu bảng theo dõi thi đua cả năm của lớp lên màn hình, tô màu những việc lớp đã làm tốt để HS nhìn lại một năm…
+Năng lực số Miền 2 (Cơ bản, bậc 1): Ở phần Phương hướng tuần 35, GV mở bảng chung còn trống trên màn hình, đại diện các tổ lần lượt lên ghi việc tổ mình nhận làm trong tuần cuối năm
 KNS: KN lập kế hoạch và quản lí chi tiêu, thời gian ở mức đơn giản.</t>
         </is>
       </c>

--- a/assets/docs/lop1/Hoat dong trai nghiem - Lop 1.xlsx
+++ b/assets/docs/lop1/Hoat dong trai nghiem - Lop 1.xlsx
@@ -923,7 +923,8 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN lập kế hoạch và quản lí chi tiêu, thời gian ở mức đơn giản.</t>
+          <t>Năng lực số 1.1 CB1b: HS hình dung và kể lại được việc sắp làm sau khi xem ảnh, video minh hoạ.
+KNS: KN lập kế hoạch và quản lí chi tiêu, thời gian ở mức đơn giản.</t>
         </is>
       </c>
     </row>

--- a/assets/docs/lop1/Hoat dong trai nghiem - Lop 1.xlsx
+++ b/assets/docs/lop1/Hoat dong trai nghiem - Lop 1.xlsx
@@ -535,7 +535,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 1: CHÀO NĂM HỌC MỚI</t>
+          <t>Chủ đề 1: Chào năm học mới</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr"/>
@@ -565,7 +565,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 1: CHÀO NĂM HỌC MỚI</t>
+          <t>Chủ đề 1: Chào năm học mới</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr"/>
@@ -599,7 +599,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 1: CHÀO NĂM HỌC MỚI</t>
+          <t>Chủ đề 1: Chào năm học mới</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr"/>
@@ -633,7 +633,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 1: CHÀO NĂM HỌC MỚI</t>
+          <t>Chủ đề 1: Chào năm học mới</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr"/>
@@ -668,7 +668,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 1: CHÀO NĂM HỌC MỚI</t>
+          <t>Chủ đề 1: Chào năm học mới</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr"/>
@@ -702,7 +702,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 1: CHÀO NĂM HỌC MỚI</t>
+          <t>Chủ đề 1: Chào năm học mới</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 1: CHÀO NĂM HỌC MỚI</t>
+          <t>Chủ đề 1: Chào năm học mới</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr"/>
@@ -768,7 +768,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 1: CHÀO NĂM HỌC MỚI</t>
+          <t>Chủ đề 1: Chào năm học mới</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr"/>
@@ -802,7 +802,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 1: CHÀO NĂM HỌC MỚI</t>
+          <t>Chủ đề 1: Chào năm học mới</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr"/>
@@ -837,7 +837,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 1: CHÀO NĂM HỌC MỚI</t>
+          <t>Chủ đề 1: Chào năm học mới</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr"/>
@@ -867,7 +867,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 1: CHÀO NĂM HỌC MỚI</t>
+          <t>Chủ đề 1: Chào năm học mới</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr"/>
@@ -901,7 +901,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 1: CHÀO NĂM HỌC MỚI</t>
+          <t>Chủ đề 1: Chào năm học mới</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr"/>
@@ -936,7 +936,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 2: EM BIẾT YÊU THƯƠNG</t>
+          <t>Chủ đề 2: Em biết yêu thương</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr"/>
@@ -966,7 +966,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 2: EM BIẾT YÊU THƯƠNG</t>
+          <t>Chủ đề 2: Em biết yêu thương</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr"/>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 2: EM BIẾT YÊU THƯƠNG</t>
+          <t>Chủ đề 2: Em biết yêu thương</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr"/>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 2: EM BIẾT YÊU THƯƠNG</t>
+          <t>Chủ đề 2: Em biết yêu thương</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr"/>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 2: EM BIẾT YÊU THƯƠNG</t>
+          <t>Chủ đề 2: Em biết yêu thương</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr"/>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 2: EM BIẾT YÊU THƯƠNG</t>
+          <t>Chủ đề 2: Em biết yêu thương</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr"/>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 2: EM BIẾT YÊU THƯƠNG</t>
+          <t>Chủ đề 2: Em biết yêu thương</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr"/>
@@ -1164,7 +1164,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 2: EM BIẾT YÊU THƯƠNG</t>
+          <t>Chủ đề 2: Em biết yêu thương</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr"/>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 2: EM BIẾT YÊU THƯƠNG</t>
+          <t>Chủ đề 2: Em biết yêu thương</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr"/>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 2: EM BIẾT YÊU THƯƠNG</t>
+          <t>Chủ đề 2: Em biết yêu thương</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr"/>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 2: EM BIẾT YÊU THƯƠNG</t>
+          <t>Chủ đề 2: Em biết yêu thương</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr"/>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 2: EM BIẾT YÊU THƯƠNG</t>
+          <t>Chủ đề 2: Em biết yêu thương</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr"/>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 3: TRUYỀN THỐNG TRƯỜNG EM</t>
+          <t>Chủ đề 3: Truyền thống trường em</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr"/>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 3: TRUYỀN THỐNG TRƯỜNG EM</t>
+          <t>Chủ đề 3: Truyền thống trường em</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr"/>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 3: TRUYỀN THỐNG TRƯỜNG EM</t>
+          <t>Chủ đề 3: Truyền thống trường em</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr"/>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 3: TRUYỀN THỐNG TRƯỜNG EM</t>
+          <t>Chủ đề 3: Truyền thống trường em</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr"/>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 3: TRUYỀN THỐNG TRƯỜNG EM</t>
+          <t>Chủ đề 3: Truyền thống trường em</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr"/>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 3: TRUYỀN THỐNG TRƯỜNG EM</t>
+          <t>Chủ đề 3: Truyền thống trường em</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr"/>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 3: TRUYỀN THỐNG TRƯỜNG EM</t>
+          <t>Chủ đề 3: Truyền thống trường em</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr"/>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 3: TRUYỀN THỐNG TRƯỜNG EM</t>
+          <t>Chủ đề 3: Truyền thống trường em</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr"/>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 3: TRUYỀN THỐNG TRƯỜNG EM</t>
+          <t>Chủ đề 3: Truyền thống trường em</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr"/>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 3: TRUYỀN THỐNG TRƯỜNG EM</t>
+          <t>Chủ đề 3: Truyền thống trường em</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr"/>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 3: TRUYỀN THỐNG TRƯỜNG EM</t>
+          <t>Chủ đề 3: Truyền thống trường em</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr"/>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 3: TRUYỀN THỐNG TRƯỜNG EM</t>
+          <t>Chủ đề 3: Truyền thống trường em</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr"/>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 4: AN TOÀN CHO EM</t>
+          <t>Chủ đề 4: An toàn cho em</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr"/>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 4: AN TOÀN CHO EM</t>
+          <t>Chủ đề 4: An toàn cho em</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr"/>
@@ -1814,7 +1814,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 4: AN TOÀN CHO EM</t>
+          <t>Chủ đề 4: An toàn cho em</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr"/>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 4: AN TOÀN CHO EM</t>
+          <t>Chủ đề 4: An toàn cho em</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr"/>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 4: AN TOÀN CHO EM</t>
+          <t>Chủ đề 4: An toàn cho em</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr"/>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 4: AN TOÀN CHO EM</t>
+          <t>Chủ đề 4: An toàn cho em</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr"/>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 4: AN TOÀN CHO EM</t>
+          <t>Chủ đề 4: An toàn cho em</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr"/>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 4: AN TOÀN CHO EM</t>
+          <t>Chủ đề 4: An toàn cho em</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr"/>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 4: AN TOÀN CHO EM</t>
+          <t>Chủ đề 4: An toàn cho em</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr"/>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 4: AN TOÀN CHO EM</t>
+          <t>Chủ đề 4: An toàn cho em</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr"/>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 4: AN TOÀN CHO EM</t>
+          <t>Chủ đề 4: An toàn cho em</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr"/>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 4: AN TOÀN CHO EM</t>
+          <t>Chủ đề 4: An toàn cho em</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr"/>
@@ -2142,7 +2142,7 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 5: EM QUÝ TRỌNG BẢN THÂN</t>
+          <t>Chủ đề 5: Em quý trọng bản thân</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr"/>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 5: EM QUÝ TRỌNG BẢN THÂN</t>
+          <t>Chủ đề 5: Em quý trọng bản thân</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr"/>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 5: EM QUÝ TRỌNG BẢN THÂN</t>
+          <t>Chủ đề 5: Em quý trọng bản thân</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr"/>
@@ -2240,7 +2240,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 5: EM QUÝ TRỌNG BẢN THÂN</t>
+          <t>Chủ đề 5: Em quý trọng bản thân</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr"/>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 5: EM QUÝ TRỌNG BẢN THÂN</t>
+          <t>Chủ đề 5: Em quý trọng bản thân</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr"/>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 5: EM QUÝ TRỌNG BẢN THÂN</t>
+          <t>Chủ đề 5: Em quý trọng bản thân</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr"/>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 5: EM QUÝ TRỌNG BẢN THÂN</t>
+          <t>Chủ đề 5: Em quý trọng bản thân</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr"/>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 5: EM QUÝ TRỌNG BẢN THÂN</t>
+          <t>Chủ đề 5: Em quý trọng bản thân</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr"/>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 5: EM QUÝ TRỌNG BẢN THÂN</t>
+          <t>Chủ đề 5: Em quý trọng bản thân</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr"/>
@@ -2433,7 +2433,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 5: EM QUÝ TRỌNG BẢN THÂN</t>
+          <t>Chủ đề 5: Em quý trọng bản thân</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr"/>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 5: EM QUÝ TRỌNG BẢN THÂN</t>
+          <t>Chủ đề 5: Em quý trọng bản thân</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr"/>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 5: EM QUÝ TRỌNG BẢN THÂN</t>
+          <t>Chủ đề 5: Em quý trọng bản thân</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr"/>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 6: VUI ĐÓN MÙA XUÂN</t>
+          <t>Chủ đề 6: Vui đón mùa xuân</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr"/>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 6: VUI ĐÓN MÙA XUÂN</t>
+          <t>Chủ đề 6: Vui đón mùa xuân</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr"/>
@@ -2600,7 +2600,7 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 6: VUI ĐÓN MÙA XUÂN</t>
+          <t>Chủ đề 6: Vui đón mùa xuân</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr"/>
@@ -2634,7 +2634,7 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 6: VUI ĐÓN MÙA XUÂN</t>
+          <t>Chủ đề 6: Vui đón mùa xuân</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr"/>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 6: VUI ĐÓN MÙA XUÂN</t>
+          <t>Chủ đề 6: Vui đón mùa xuân</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr"/>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 6: VUI ĐÓN MÙA XUÂN</t>
+          <t>Chủ đề 6: Vui đón mùa xuân</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr"/>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 6: VUI ĐÓN MÙA XUÂN</t>
+          <t>Chủ đề 6: Vui đón mùa xuân</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr"/>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 6: VUI ĐÓN MÙA XUÂN</t>
+          <t>Chủ đề 6: Vui đón mùa xuân</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr"/>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 6: VUI ĐÓN MÙA XUÂN</t>
+          <t>Chủ đề 6: Vui đón mùa xuân</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr"/>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 6: VUI ĐÓN MÙA XUÂN</t>
+          <t>Chủ đề 6: Vui đón mùa xuân</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr"/>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 6: VUI ĐÓN MÙA XUÂN</t>
+          <t>Chủ đề 6: Vui đón mùa xuân</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr"/>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 6: VUI ĐÓN MÙA XUÂN</t>
+          <t>Chủ đề 6: Vui đón mùa xuân</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr"/>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 7: THAM GIA HOẠT ĐỘNG CỘNG ĐỒNG</t>
+          <t>Chủ đề 7: Tham gia hoạt động cộng đồng</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr"/>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 7: THAM GIA HOẠT ĐỘNG CỘNG ĐỒNG</t>
+          <t>Chủ đề 7: Tham gia hoạt động cộng đồng</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr"/>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 7: THAM GIA HOẠT ĐỘNG CỘNG ĐỒNG</t>
+          <t>Chủ đề 7: Tham gia hoạt động cộng đồng</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr"/>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 7: THAM GIA HOẠT ĐỘNG CỘNG ĐỒNG</t>
+          <t>Chủ đề 7: Tham gia hoạt động cộng đồng</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr"/>
@@ -3070,7 +3070,7 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 7: THAM GIA HOẠT ĐỘNG CỘNG ĐỒNG</t>
+          <t>Chủ đề 7: Tham gia hoạt động cộng đồng</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr"/>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 7: THAM GIA HOẠT ĐỘNG CỘNG ĐỒNG</t>
+          <t>Chủ đề 7: Tham gia hoạt động cộng đồng</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr"/>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 7: THAM GIA HOẠT ĐỘNG CỘNG ĐỒNG</t>
+          <t>Chủ đề 7: Tham gia hoạt động cộng đồng</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr"/>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 7: THAM GIA HOẠT ĐỘNG CỘNG ĐỒNG</t>
+          <t>Chủ đề 7: Tham gia hoạt động cộng đồng</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr"/>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 7: THAM GIA HOẠT ĐỘNG CỘNG ĐỒNG</t>
+          <t>Chủ đề 7: Tham gia hoạt động cộng đồng</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr"/>
@@ -3228,7 +3228,7 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 7: THAM GIA HOẠT ĐỘNG CỘNG ĐỒNG</t>
+          <t>Chủ đề 7: Tham gia hoạt động cộng đồng</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr"/>
@@ -3258,7 +3258,7 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 7: THAM GIA HOẠT ĐỘNG CỘNG ĐỒNG</t>
+          <t>Chủ đề 7: Tham gia hoạt động cộng đồng</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr"/>
@@ -3292,7 +3292,7 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 7: THAM GIA HOẠT ĐỘNG CỘNG ĐỒNG</t>
+          <t>Chủ đề 7: Tham gia hoạt động cộng đồng</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr"/>
@@ -3327,7 +3327,7 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 8: QUÊ HƯƠNG TƯƠI ĐẸP</t>
+          <t>Chủ đề 8: Quê hương tươi đẹp</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr"/>
@@ -3361,7 +3361,7 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 8: QUÊ HƯƠNG TƯƠI ĐẸP</t>
+          <t>Chủ đề 8: Quê hương tươi đẹp</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr"/>
@@ -3395,7 +3395,7 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 8: QUÊ HƯƠNG TƯƠI ĐẸP</t>
+          <t>Chủ đề 8: Quê hương tươi đẹp</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr"/>
@@ -3429,7 +3429,7 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 8: QUÊ HƯƠNG TƯƠI ĐẸP</t>
+          <t>Chủ đề 8: Quê hương tươi đẹp</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr"/>
@@ -3459,7 +3459,7 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 8: QUÊ HƯƠNG TƯƠI ĐẸP</t>
+          <t>Chủ đề 8: Quê hương tươi đẹp</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr"/>
@@ -3493,7 +3493,7 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 8: QUÊ HƯƠNG TƯƠI ĐẸP</t>
+          <t>Chủ đề 8: Quê hương tươi đẹp</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr"/>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 8: QUÊ HƯƠNG TƯƠI ĐẸP</t>
+          <t>Chủ đề 8: Quê hương tươi đẹp</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr"/>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 8: QUÊ HƯƠNG TƯƠI ĐẸP</t>
+          <t>Chủ đề 8: Quê hương tươi đẹp</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr"/>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 8: QUÊ HƯƠNG TƯƠI ĐẸP</t>
+          <t>Chủ đề 8: Quê hương tươi đẹp</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr"/>
@@ -3633,7 +3633,7 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 8: QUÊ HƯƠNG TƯƠI ĐẸP</t>
+          <t>Chủ đề 8: Quê hương tươi đẹp</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr"/>
@@ -3667,7 +3667,7 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 8: QUÊ HƯƠNG TƯƠI ĐẸP</t>
+          <t>Chủ đề 8: Quê hương tươi đẹp</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr"/>
@@ -3702,7 +3702,7 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 8: QUÊ HƯƠNG TƯƠI ĐẸP</t>
+          <t>Chủ đề 8: Quê hương tươi đẹp</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr"/>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 9: EM BẢO VỆ MÔI TRƯỜNG</t>
+          <t>Chủ đề 9: Em bảo vệ môi trường</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr"/>
@@ -3772,7 +3772,7 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 9: EM BẢO VỆ MÔI TRƯỜNG</t>
+          <t>Chủ đề 9: Em bảo vệ môi trường</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr"/>
@@ -3808,7 +3808,7 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 9: EM BẢO VỆ MÔI TRƯỜNG</t>
+          <t>Chủ đề 9: Em bảo vệ môi trường</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr"/>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 9: EM BẢO VỆ MÔI TRƯỜNG</t>
+          <t>Chủ đề 9: Em bảo vệ môi trường</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr"/>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 9: EM BẢO VỆ MÔI TRƯỜNG</t>
+          <t>Chủ đề 9: Em bảo vệ môi trường</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr"/>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 9: EM BẢO VỆ MÔI TRƯỜNG</t>
+          <t>Chủ đề 9: Em bảo vệ môi trường</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr"/>
@@ -3945,7 +3945,7 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 9: EM BẢO VỆ MÔI TRƯỜNG</t>
+          <t>Chủ đề 9: Em bảo vệ môi trường</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr"/>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 9: EM BẢO VỆ MÔI TRƯỜNG</t>
+          <t>Chủ đề 9: Em bảo vệ môi trường</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr"/>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>CHỦ ĐỀ 9: EM BẢO VỆ MÔI TRƯỜNG</t>
+          <t>Chủ đề 9: Em bảo vệ môi trường</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr"/>
